--- a/res_summer_sequencing.xlsx
+++ b/res_summer_sequencing.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -13996,6 +13996,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/res_summer_sequencing.xlsx
+++ b/res_summer_sequencing.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z169"/>
+  <dimension ref="A1:V169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,26 +534,6 @@
           <t>c_el</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -621,18 +601,6 @@
       </c>
       <c r="V2" t="n">
         <v>0.16</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -702,18 +670,6 @@
       <c r="V3" t="n">
         <v>0.16</v>
       </c>
-      <c r="W3" t="n">
-        <v>3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -782,18 +738,6 @@
       <c r="V4" t="n">
         <v>0.16</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -862,18 +806,6 @@
       <c r="V5" t="n">
         <v>0.16</v>
       </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -942,18 +874,6 @@
       <c r="V6" t="n">
         <v>0.16</v>
       </c>
-      <c r="W6" t="n">
-        <v>3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1022,18 +942,6 @@
       <c r="V7" t="n">
         <v>0.16</v>
       </c>
-      <c r="W7" t="n">
-        <v>3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1102,18 +1010,6 @@
       <c r="V8" t="n">
         <v>0.16</v>
       </c>
-      <c r="W8" t="n">
-        <v>3</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1182,18 +1078,6 @@
       <c r="V9" t="n">
         <v>0.16</v>
       </c>
-      <c r="W9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1262,18 +1146,6 @@
       <c r="V10" t="n">
         <v>0.25</v>
       </c>
-      <c r="W10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1342,18 +1214,6 @@
       <c r="V11" t="n">
         <v>0.25</v>
       </c>
-      <c r="W11" t="n">
-        <v>3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1422,18 +1282,6 @@
       <c r="V12" t="n">
         <v>0.25</v>
       </c>
-      <c r="W12" t="n">
-        <v>3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1502,18 +1350,6 @@
       <c r="V13" t="n">
         <v>0.25</v>
       </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1582,18 +1418,6 @@
       <c r="V14" t="n">
         <v>0.25</v>
       </c>
-      <c r="W14" t="n">
-        <v>3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1662,18 +1486,6 @@
       <c r="V15" t="n">
         <v>0.25</v>
       </c>
-      <c r="W15" t="n">
-        <v>3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1742,18 +1554,6 @@
       <c r="V16" t="n">
         <v>0.25</v>
       </c>
-      <c r="W16" t="n">
-        <v>3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1822,18 +1622,6 @@
       <c r="V17" t="n">
         <v>0.25</v>
       </c>
-      <c r="W17" t="n">
-        <v>3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1902,18 +1690,6 @@
       <c r="V18" t="n">
         <v>0.25</v>
       </c>
-      <c r="W18" t="n">
-        <v>3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1982,18 +1758,6 @@
       <c r="V19" t="n">
         <v>0.25</v>
       </c>
-      <c r="W19" t="n">
-        <v>3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2062,18 +1826,6 @@
       <c r="V20" t="n">
         <v>0.25</v>
       </c>
-      <c r="W20" t="n">
-        <v>3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2142,18 +1894,6 @@
       <c r="V21" t="n">
         <v>0.25</v>
       </c>
-      <c r="W21" t="n">
-        <v>3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2222,18 +1962,6 @@
       <c r="V22" t="n">
         <v>0.25</v>
       </c>
-      <c r="W22" t="n">
-        <v>3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2302,18 +2030,6 @@
       <c r="V23" t="n">
         <v>0.16</v>
       </c>
-      <c r="W23" t="n">
-        <v>3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2382,18 +2098,6 @@
       <c r="V24" t="n">
         <v>0.16</v>
       </c>
-      <c r="W24" t="n">
-        <v>3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2462,18 +2166,6 @@
       <c r="V25" t="n">
         <v>0.16</v>
       </c>
-      <c r="W25" t="n">
-        <v>3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2542,18 +2234,6 @@
       <c r="V26" t="n">
         <v>0.16</v>
       </c>
-      <c r="W26" t="n">
-        <v>3</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2622,18 +2302,6 @@
       <c r="V27" t="n">
         <v>0.16</v>
       </c>
-      <c r="W27" t="n">
-        <v>3</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2702,18 +2370,6 @@
       <c r="V28" t="n">
         <v>0.16</v>
       </c>
-      <c r="W28" t="n">
-        <v>3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2782,18 +2438,6 @@
       <c r="V29" t="n">
         <v>0.16</v>
       </c>
-      <c r="W29" t="n">
-        <v>3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2862,18 +2506,6 @@
       <c r="V30" t="n">
         <v>0.16</v>
       </c>
-      <c r="W30" t="n">
-        <v>3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2942,18 +2574,6 @@
       <c r="V31" t="n">
         <v>0.16</v>
       </c>
-      <c r="W31" t="n">
-        <v>3</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3022,18 +2642,6 @@
       <c r="V32" t="n">
         <v>0.16</v>
       </c>
-      <c r="W32" t="n">
-        <v>3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3102,18 +2710,6 @@
       <c r="V33" t="n">
         <v>0.16</v>
       </c>
-      <c r="W33" t="n">
-        <v>3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3182,18 +2778,6 @@
       <c r="V34" t="n">
         <v>0.25</v>
       </c>
-      <c r="W34" t="n">
-        <v>3</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3262,18 +2846,6 @@
       <c r="V35" t="n">
         <v>0.25</v>
       </c>
-      <c r="W35" t="n">
-        <v>3</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3342,18 +2914,6 @@
       <c r="V36" t="n">
         <v>0.25</v>
       </c>
-      <c r="W36" t="n">
-        <v>3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3422,18 +2982,6 @@
       <c r="V37" t="n">
         <v>0.25</v>
       </c>
-      <c r="W37" t="n">
-        <v>3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3502,18 +3050,6 @@
       <c r="V38" t="n">
         <v>0.25</v>
       </c>
-      <c r="W38" t="n">
-        <v>3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3582,18 +3118,6 @@
       <c r="V39" t="n">
         <v>0.25</v>
       </c>
-      <c r="W39" t="n">
-        <v>3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3662,18 +3186,6 @@
       <c r="V40" t="n">
         <v>0.25</v>
       </c>
-      <c r="W40" t="n">
-        <v>3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3742,18 +3254,6 @@
       <c r="V41" t="n">
         <v>0.25</v>
       </c>
-      <c r="W41" t="n">
-        <v>3</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3822,18 +3322,6 @@
       <c r="V42" t="n">
         <v>0.25</v>
       </c>
-      <c r="W42" t="n">
-        <v>3</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3902,18 +3390,6 @@
       <c r="V43" t="n">
         <v>0.25</v>
       </c>
-      <c r="W43" t="n">
-        <v>3</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3982,18 +3458,6 @@
       <c r="V44" t="n">
         <v>0.25</v>
       </c>
-      <c r="W44" t="n">
-        <v>3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4062,18 +3526,6 @@
       <c r="V45" t="n">
         <v>0.25</v>
       </c>
-      <c r="W45" t="n">
-        <v>3</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4142,18 +3594,6 @@
       <c r="V46" t="n">
         <v>0.25</v>
       </c>
-      <c r="W46" t="n">
-        <v>3</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4222,18 +3662,6 @@
       <c r="V47" t="n">
         <v>0.16</v>
       </c>
-      <c r="W47" t="n">
-        <v>3</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4302,18 +3730,6 @@
       <c r="V48" t="n">
         <v>0.16</v>
       </c>
-      <c r="W48" t="n">
-        <v>3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4382,18 +3798,6 @@
       <c r="V49" t="n">
         <v>0.16</v>
       </c>
-      <c r="W49" t="n">
-        <v>3</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4462,18 +3866,6 @@
       <c r="V50" t="n">
         <v>0.16</v>
       </c>
-      <c r="W50" t="n">
-        <v>3</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -4542,18 +3934,6 @@
       <c r="V51" t="n">
         <v>0.16</v>
       </c>
-      <c r="W51" t="n">
-        <v>3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -4622,18 +4002,6 @@
       <c r="V52" t="n">
         <v>0.16</v>
       </c>
-      <c r="W52" t="n">
-        <v>3</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -4702,18 +4070,6 @@
       <c r="V53" t="n">
         <v>0.16</v>
       </c>
-      <c r="W53" t="n">
-        <v>3</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -4782,18 +4138,6 @@
       <c r="V54" t="n">
         <v>0.16</v>
       </c>
-      <c r="W54" t="n">
-        <v>3</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -4862,18 +4206,6 @@
       <c r="V55" t="n">
         <v>0.16</v>
       </c>
-      <c r="W55" t="n">
-        <v>3</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -4942,18 +4274,6 @@
       <c r="V56" t="n">
         <v>0.16</v>
       </c>
-      <c r="W56" t="n">
-        <v>3</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5022,18 +4342,6 @@
       <c r="V57" t="n">
         <v>0.16</v>
       </c>
-      <c r="W57" t="n">
-        <v>3</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5102,18 +4410,6 @@
       <c r="V58" t="n">
         <v>0.25</v>
       </c>
-      <c r="W58" t="n">
-        <v>3</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5182,18 +4478,6 @@
       <c r="V59" t="n">
         <v>0.25</v>
       </c>
-      <c r="W59" t="n">
-        <v>3</v>
-      </c>
-      <c r="X59" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5262,18 +4546,6 @@
       <c r="V60" t="n">
         <v>0.25</v>
       </c>
-      <c r="W60" t="n">
-        <v>3</v>
-      </c>
-      <c r="X60" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5342,18 +4614,6 @@
       <c r="V61" t="n">
         <v>0.25</v>
       </c>
-      <c r="W61" t="n">
-        <v>3</v>
-      </c>
-      <c r="X61" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -5422,18 +4682,6 @@
       <c r="V62" t="n">
         <v>0.25</v>
       </c>
-      <c r="W62" t="n">
-        <v>3</v>
-      </c>
-      <c r="X62" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -5502,18 +4750,6 @@
       <c r="V63" t="n">
         <v>0.25</v>
       </c>
-      <c r="W63" t="n">
-        <v>3</v>
-      </c>
-      <c r="X63" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -5582,18 +4818,6 @@
       <c r="V64" t="n">
         <v>0.25</v>
       </c>
-      <c r="W64" t="n">
-        <v>3</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -5662,18 +4886,6 @@
       <c r="V65" t="n">
         <v>0.25</v>
       </c>
-      <c r="W65" t="n">
-        <v>3</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -5742,18 +4954,6 @@
       <c r="V66" t="n">
         <v>0.25</v>
       </c>
-      <c r="W66" t="n">
-        <v>3</v>
-      </c>
-      <c r="X66" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -5822,18 +5022,6 @@
       <c r="V67" t="n">
         <v>0.25</v>
       </c>
-      <c r="W67" t="n">
-        <v>3</v>
-      </c>
-      <c r="X67" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5902,18 +5090,6 @@
       <c r="V68" t="n">
         <v>0.25</v>
       </c>
-      <c r="W68" t="n">
-        <v>3</v>
-      </c>
-      <c r="X68" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -5982,18 +5158,6 @@
       <c r="V69" t="n">
         <v>0.25</v>
       </c>
-      <c r="W69" t="n">
-        <v>3</v>
-      </c>
-      <c r="X69" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -6062,18 +5226,6 @@
       <c r="V70" t="n">
         <v>0.25</v>
       </c>
-      <c r="W70" t="n">
-        <v>3</v>
-      </c>
-      <c r="X70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -6142,18 +5294,6 @@
       <c r="V71" t="n">
         <v>0.16</v>
       </c>
-      <c r="W71" t="n">
-        <v>3</v>
-      </c>
-      <c r="X71" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -6222,18 +5362,6 @@
       <c r="V72" t="n">
         <v>0.16</v>
       </c>
-      <c r="W72" t="n">
-        <v>3</v>
-      </c>
-      <c r="X72" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -6302,18 +5430,6 @@
       <c r="V73" t="n">
         <v>0.16</v>
       </c>
-      <c r="W73" t="n">
-        <v>3</v>
-      </c>
-      <c r="X73" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -6382,18 +5498,6 @@
       <c r="V74" t="n">
         <v>0.16</v>
       </c>
-      <c r="W74" t="n">
-        <v>3</v>
-      </c>
-      <c r="X74" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -6462,18 +5566,6 @@
       <c r="V75" t="n">
         <v>0.16</v>
       </c>
-      <c r="W75" t="n">
-        <v>3</v>
-      </c>
-      <c r="X75" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -6542,18 +5634,6 @@
       <c r="V76" t="n">
         <v>0.16</v>
       </c>
-      <c r="W76" t="n">
-        <v>3</v>
-      </c>
-      <c r="X76" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -6622,18 +5702,6 @@
       <c r="V77" t="n">
         <v>0.16</v>
       </c>
-      <c r="W77" t="n">
-        <v>3</v>
-      </c>
-      <c r="X77" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -6702,18 +5770,6 @@
       <c r="V78" t="n">
         <v>0.16</v>
       </c>
-      <c r="W78" t="n">
-        <v>3</v>
-      </c>
-      <c r="X78" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -6782,18 +5838,6 @@
       <c r="V79" t="n">
         <v>0.16</v>
       </c>
-      <c r="W79" t="n">
-        <v>3</v>
-      </c>
-      <c r="X79" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -6862,18 +5906,6 @@
       <c r="V80" t="n">
         <v>0.16</v>
       </c>
-      <c r="W80" t="n">
-        <v>3</v>
-      </c>
-      <c r="X80" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -6942,18 +5974,6 @@
       <c r="V81" t="n">
         <v>0.16</v>
       </c>
-      <c r="W81" t="n">
-        <v>3</v>
-      </c>
-      <c r="X81" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -7022,18 +6042,6 @@
       <c r="V82" t="n">
         <v>0.25</v>
       </c>
-      <c r="W82" t="n">
-        <v>3</v>
-      </c>
-      <c r="X82" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -7102,18 +6110,6 @@
       <c r="V83" t="n">
         <v>0.25</v>
       </c>
-      <c r="W83" t="n">
-        <v>3</v>
-      </c>
-      <c r="X83" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -7182,18 +6178,6 @@
       <c r="V84" t="n">
         <v>0.25</v>
       </c>
-      <c r="W84" t="n">
-        <v>3</v>
-      </c>
-      <c r="X84" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -7262,18 +6246,6 @@
       <c r="V85" t="n">
         <v>0.25</v>
       </c>
-      <c r="W85" t="n">
-        <v>3</v>
-      </c>
-      <c r="X85" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -7342,18 +6314,6 @@
       <c r="V86" t="n">
         <v>0.25</v>
       </c>
-      <c r="W86" t="n">
-        <v>3</v>
-      </c>
-      <c r="X86" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -7422,18 +6382,6 @@
       <c r="V87" t="n">
         <v>0.25</v>
       </c>
-      <c r="W87" t="n">
-        <v>3</v>
-      </c>
-      <c r="X87" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -7502,18 +6450,6 @@
       <c r="V88" t="n">
         <v>0.25</v>
       </c>
-      <c r="W88" t="n">
-        <v>3</v>
-      </c>
-      <c r="X88" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -7582,18 +6518,6 @@
       <c r="V89" t="n">
         <v>0.25</v>
       </c>
-      <c r="W89" t="n">
-        <v>3</v>
-      </c>
-      <c r="X89" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -7662,18 +6586,6 @@
       <c r="V90" t="n">
         <v>0.25</v>
       </c>
-      <c r="W90" t="n">
-        <v>3</v>
-      </c>
-      <c r="X90" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -7742,18 +6654,6 @@
       <c r="V91" t="n">
         <v>0.25</v>
       </c>
-      <c r="W91" t="n">
-        <v>3</v>
-      </c>
-      <c r="X91" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -7822,18 +6722,6 @@
       <c r="V92" t="n">
         <v>0.25</v>
       </c>
-      <c r="W92" t="n">
-        <v>3</v>
-      </c>
-      <c r="X92" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -7902,18 +6790,6 @@
       <c r="V93" t="n">
         <v>0.25</v>
       </c>
-      <c r="W93" t="n">
-        <v>3</v>
-      </c>
-      <c r="X93" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -7982,18 +6858,6 @@
       <c r="V94" t="n">
         <v>0.25</v>
       </c>
-      <c r="W94" t="n">
-        <v>3</v>
-      </c>
-      <c r="X94" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -8062,18 +6926,6 @@
       <c r="V95" t="n">
         <v>0.16</v>
       </c>
-      <c r="W95" t="n">
-        <v>3</v>
-      </c>
-      <c r="X95" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -8142,18 +6994,6 @@
       <c r="V96" t="n">
         <v>0.16</v>
       </c>
-      <c r="W96" t="n">
-        <v>3</v>
-      </c>
-      <c r="X96" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -8222,18 +7062,6 @@
       <c r="V97" t="n">
         <v>0.16</v>
       </c>
-      <c r="W97" t="n">
-        <v>3</v>
-      </c>
-      <c r="X97" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -8302,18 +7130,6 @@
       <c r="V98" t="n">
         <v>0.16</v>
       </c>
-      <c r="W98" t="n">
-        <v>3</v>
-      </c>
-      <c r="X98" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -8382,18 +7198,6 @@
       <c r="V99" t="n">
         <v>0.16</v>
       </c>
-      <c r="W99" t="n">
-        <v>3</v>
-      </c>
-      <c r="X99" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -8462,18 +7266,6 @@
       <c r="V100" t="n">
         <v>0.16</v>
       </c>
-      <c r="W100" t="n">
-        <v>3</v>
-      </c>
-      <c r="X100" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -8542,18 +7334,6 @@
       <c r="V101" t="n">
         <v>0.16</v>
       </c>
-      <c r="W101" t="n">
-        <v>3</v>
-      </c>
-      <c r="X101" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -8622,18 +7402,6 @@
       <c r="V102" t="n">
         <v>0.16</v>
       </c>
-      <c r="W102" t="n">
-        <v>3</v>
-      </c>
-      <c r="X102" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -8702,18 +7470,6 @@
       <c r="V103" t="n">
         <v>0.16</v>
       </c>
-      <c r="W103" t="n">
-        <v>3</v>
-      </c>
-      <c r="X103" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -8782,18 +7538,6 @@
       <c r="V104" t="n">
         <v>0.16</v>
       </c>
-      <c r="W104" t="n">
-        <v>3</v>
-      </c>
-      <c r="X104" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -8862,18 +7606,6 @@
       <c r="V105" t="n">
         <v>0.16</v>
       </c>
-      <c r="W105" t="n">
-        <v>3</v>
-      </c>
-      <c r="X105" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -8942,18 +7674,6 @@
       <c r="V106" t="n">
         <v>0.25</v>
       </c>
-      <c r="W106" t="n">
-        <v>3</v>
-      </c>
-      <c r="X106" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -9022,18 +7742,6 @@
       <c r="V107" t="n">
         <v>0.25</v>
       </c>
-      <c r="W107" t="n">
-        <v>3</v>
-      </c>
-      <c r="X107" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -9102,18 +7810,6 @@
       <c r="V108" t="n">
         <v>0.25</v>
       </c>
-      <c r="W108" t="n">
-        <v>3</v>
-      </c>
-      <c r="X108" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -9182,18 +7878,6 @@
       <c r="V109" t="n">
         <v>0.25</v>
       </c>
-      <c r="W109" t="n">
-        <v>3</v>
-      </c>
-      <c r="X109" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -9262,18 +7946,6 @@
       <c r="V110" t="n">
         <v>0.25</v>
       </c>
-      <c r="W110" t="n">
-        <v>3</v>
-      </c>
-      <c r="X110" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -9342,18 +8014,6 @@
       <c r="V111" t="n">
         <v>0.25</v>
       </c>
-      <c r="W111" t="n">
-        <v>3</v>
-      </c>
-      <c r="X111" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -9422,18 +8082,6 @@
       <c r="V112" t="n">
         <v>0.25</v>
       </c>
-      <c r="W112" t="n">
-        <v>3</v>
-      </c>
-      <c r="X112" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -9502,18 +8150,6 @@
       <c r="V113" t="n">
         <v>0.25</v>
       </c>
-      <c r="W113" t="n">
-        <v>3</v>
-      </c>
-      <c r="X113" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -9582,18 +8218,6 @@
       <c r="V114" t="n">
         <v>0.25</v>
       </c>
-      <c r="W114" t="n">
-        <v>3</v>
-      </c>
-      <c r="X114" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -9662,18 +8286,6 @@
       <c r="V115" t="n">
         <v>0.25</v>
       </c>
-      <c r="W115" t="n">
-        <v>3</v>
-      </c>
-      <c r="X115" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -9742,18 +8354,6 @@
       <c r="V116" t="n">
         <v>0.25</v>
       </c>
-      <c r="W116" t="n">
-        <v>3</v>
-      </c>
-      <c r="X116" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -9822,18 +8422,6 @@
       <c r="V117" t="n">
         <v>0.25</v>
       </c>
-      <c r="W117" t="n">
-        <v>3</v>
-      </c>
-      <c r="X117" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -9902,18 +8490,6 @@
       <c r="V118" t="n">
         <v>0.25</v>
       </c>
-      <c r="W118" t="n">
-        <v>3</v>
-      </c>
-      <c r="X118" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -9982,18 +8558,6 @@
       <c r="V119" t="n">
         <v>0.16</v>
       </c>
-      <c r="W119" t="n">
-        <v>3</v>
-      </c>
-      <c r="X119" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z119" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -10062,18 +8626,6 @@
       <c r="V120" t="n">
         <v>0.16</v>
       </c>
-      <c r="W120" t="n">
-        <v>3</v>
-      </c>
-      <c r="X120" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -10142,18 +8694,6 @@
       <c r="V121" t="n">
         <v>0.16</v>
       </c>
-      <c r="W121" t="n">
-        <v>3</v>
-      </c>
-      <c r="X121" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -10222,18 +8762,6 @@
       <c r="V122" t="n">
         <v>0.16</v>
       </c>
-      <c r="W122" t="n">
-        <v>3</v>
-      </c>
-      <c r="X122" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -10302,18 +8830,6 @@
       <c r="V123" t="n">
         <v>0.16</v>
       </c>
-      <c r="W123" t="n">
-        <v>3</v>
-      </c>
-      <c r="X123" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -10382,18 +8898,6 @@
       <c r="V124" t="n">
         <v>0.16</v>
       </c>
-      <c r="W124" t="n">
-        <v>3</v>
-      </c>
-      <c r="X124" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -10462,18 +8966,6 @@
       <c r="V125" t="n">
         <v>0.16</v>
       </c>
-      <c r="W125" t="n">
-        <v>3</v>
-      </c>
-      <c r="X125" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -10542,18 +9034,6 @@
       <c r="V126" t="n">
         <v>0.16</v>
       </c>
-      <c r="W126" t="n">
-        <v>3</v>
-      </c>
-      <c r="X126" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -10622,18 +9102,6 @@
       <c r="V127" t="n">
         <v>0.16</v>
       </c>
-      <c r="W127" t="n">
-        <v>3</v>
-      </c>
-      <c r="X127" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -10702,18 +9170,6 @@
       <c r="V128" t="n">
         <v>0.16</v>
       </c>
-      <c r="W128" t="n">
-        <v>3</v>
-      </c>
-      <c r="X128" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -10782,18 +9238,6 @@
       <c r="V129" t="n">
         <v>0.16</v>
       </c>
-      <c r="W129" t="n">
-        <v>3</v>
-      </c>
-      <c r="X129" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -10862,18 +9306,6 @@
       <c r="V130" t="n">
         <v>0.25</v>
       </c>
-      <c r="W130" t="n">
-        <v>3</v>
-      </c>
-      <c r="X130" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -10942,18 +9374,6 @@
       <c r="V131" t="n">
         <v>0.25</v>
       </c>
-      <c r="W131" t="n">
-        <v>3</v>
-      </c>
-      <c r="X131" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -11022,18 +9442,6 @@
       <c r="V132" t="n">
         <v>0.25</v>
       </c>
-      <c r="W132" t="n">
-        <v>3</v>
-      </c>
-      <c r="X132" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -11102,18 +9510,6 @@
       <c r="V133" t="n">
         <v>0.25</v>
       </c>
-      <c r="W133" t="n">
-        <v>3</v>
-      </c>
-      <c r="X133" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -11182,18 +9578,6 @@
       <c r="V134" t="n">
         <v>0.25</v>
       </c>
-      <c r="W134" t="n">
-        <v>3</v>
-      </c>
-      <c r="X134" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -11262,18 +9646,6 @@
       <c r="V135" t="n">
         <v>0.25</v>
       </c>
-      <c r="W135" t="n">
-        <v>3</v>
-      </c>
-      <c r="X135" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -11342,18 +9714,6 @@
       <c r="V136" t="n">
         <v>0.25</v>
       </c>
-      <c r="W136" t="n">
-        <v>3</v>
-      </c>
-      <c r="X136" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -11422,18 +9782,6 @@
       <c r="V137" t="n">
         <v>0.25</v>
       </c>
-      <c r="W137" t="n">
-        <v>3</v>
-      </c>
-      <c r="X137" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -11502,18 +9850,6 @@
       <c r="V138" t="n">
         <v>0.25</v>
       </c>
-      <c r="W138" t="n">
-        <v>3</v>
-      </c>
-      <c r="X138" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -11582,18 +9918,6 @@
       <c r="V139" t="n">
         <v>0.25</v>
       </c>
-      <c r="W139" t="n">
-        <v>3</v>
-      </c>
-      <c r="X139" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -11662,18 +9986,6 @@
       <c r="V140" t="n">
         <v>0.25</v>
       </c>
-      <c r="W140" t="n">
-        <v>3</v>
-      </c>
-      <c r="X140" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -11742,18 +10054,6 @@
       <c r="V141" t="n">
         <v>0.25</v>
       </c>
-      <c r="W141" t="n">
-        <v>3</v>
-      </c>
-      <c r="X141" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -11822,18 +10122,6 @@
       <c r="V142" t="n">
         <v>0.25</v>
       </c>
-      <c r="W142" t="n">
-        <v>3</v>
-      </c>
-      <c r="X142" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -11902,18 +10190,6 @@
       <c r="V143" t="n">
         <v>0.16</v>
       </c>
-      <c r="W143" t="n">
-        <v>3</v>
-      </c>
-      <c r="X143" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -11982,18 +10258,6 @@
       <c r="V144" t="n">
         <v>0.16</v>
       </c>
-      <c r="W144" t="n">
-        <v>3</v>
-      </c>
-      <c r="X144" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -12062,18 +10326,6 @@
       <c r="V145" t="n">
         <v>0.16</v>
       </c>
-      <c r="W145" t="n">
-        <v>3</v>
-      </c>
-      <c r="X145" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -12142,18 +10394,6 @@
       <c r="V146" t="n">
         <v>0.16</v>
       </c>
-      <c r="W146" t="n">
-        <v>3</v>
-      </c>
-      <c r="X146" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y146" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -12222,18 +10462,6 @@
       <c r="V147" t="n">
         <v>0.16</v>
       </c>
-      <c r="W147" t="n">
-        <v>3</v>
-      </c>
-      <c r="X147" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -12302,18 +10530,6 @@
       <c r="V148" t="n">
         <v>0.16</v>
       </c>
-      <c r="W148" t="n">
-        <v>3</v>
-      </c>
-      <c r="X148" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -12382,18 +10598,6 @@
       <c r="V149" t="n">
         <v>0.16</v>
       </c>
-      <c r="W149" t="n">
-        <v>3</v>
-      </c>
-      <c r="X149" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -12462,18 +10666,6 @@
       <c r="V150" t="n">
         <v>0.16</v>
       </c>
-      <c r="W150" t="n">
-        <v>3</v>
-      </c>
-      <c r="X150" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -12542,18 +10734,6 @@
       <c r="V151" t="n">
         <v>0.16</v>
       </c>
-      <c r="W151" t="n">
-        <v>3</v>
-      </c>
-      <c r="X151" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -12622,18 +10802,6 @@
       <c r="V152" t="n">
         <v>0.16</v>
       </c>
-      <c r="W152" t="n">
-        <v>3</v>
-      </c>
-      <c r="X152" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y152" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -12702,18 +10870,6 @@
       <c r="V153" t="n">
         <v>0.16</v>
       </c>
-      <c r="W153" t="n">
-        <v>3</v>
-      </c>
-      <c r="X153" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y153" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -12782,18 +10938,6 @@
       <c r="V154" t="n">
         <v>0.25</v>
       </c>
-      <c r="W154" t="n">
-        <v>3</v>
-      </c>
-      <c r="X154" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -12862,18 +11006,6 @@
       <c r="V155" t="n">
         <v>0.25</v>
       </c>
-      <c r="W155" t="n">
-        <v>3</v>
-      </c>
-      <c r="X155" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -12942,18 +11074,6 @@
       <c r="V156" t="n">
         <v>0.25</v>
       </c>
-      <c r="W156" t="n">
-        <v>3</v>
-      </c>
-      <c r="X156" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -13022,18 +11142,6 @@
       <c r="V157" t="n">
         <v>0.25</v>
       </c>
-      <c r="W157" t="n">
-        <v>3</v>
-      </c>
-      <c r="X157" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -13102,18 +11210,6 @@
       <c r="V158" t="n">
         <v>0.25</v>
       </c>
-      <c r="W158" t="n">
-        <v>3</v>
-      </c>
-      <c r="X158" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y158" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z158" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -13182,18 +11278,6 @@
       <c r="V159" t="n">
         <v>0.25</v>
       </c>
-      <c r="W159" t="n">
-        <v>3</v>
-      </c>
-      <c r="X159" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y159" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z159" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -13262,18 +11346,6 @@
       <c r="V160" t="n">
         <v>0.25</v>
       </c>
-      <c r="W160" t="n">
-        <v>3</v>
-      </c>
-      <c r="X160" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -13342,18 +11414,6 @@
       <c r="V161" t="n">
         <v>0.25</v>
       </c>
-      <c r="W161" t="n">
-        <v>3</v>
-      </c>
-      <c r="X161" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -13422,18 +11482,6 @@
       <c r="V162" t="n">
         <v>0.25</v>
       </c>
-      <c r="W162" t="n">
-        <v>3</v>
-      </c>
-      <c r="X162" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -13502,18 +11550,6 @@
       <c r="V163" t="n">
         <v>0.25</v>
       </c>
-      <c r="W163" t="n">
-        <v>3</v>
-      </c>
-      <c r="X163" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -13582,18 +11618,6 @@
       <c r="V164" t="n">
         <v>0.25</v>
       </c>
-      <c r="W164" t="n">
-        <v>3</v>
-      </c>
-      <c r="X164" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -13662,18 +11686,6 @@
       <c r="V165" t="n">
         <v>0.25</v>
       </c>
-      <c r="W165" t="n">
-        <v>3</v>
-      </c>
-      <c r="X165" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y165" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -13742,18 +11754,6 @@
       <c r="V166" t="n">
         <v>0.25</v>
       </c>
-      <c r="W166" t="n">
-        <v>3</v>
-      </c>
-      <c r="X166" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -13822,18 +11822,6 @@
       <c r="V167" t="n">
         <v>0.16</v>
       </c>
-      <c r="W167" t="n">
-        <v>3</v>
-      </c>
-      <c r="X167" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y167" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z167" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -13902,18 +11890,6 @@
       <c r="V168" t="n">
         <v>0.16</v>
       </c>
-      <c r="W168" t="n">
-        <v>3</v>
-      </c>
-      <c r="X168" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y168" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z168" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -13982,20 +11958,8 @@
       <c r="V169" t="n">
         <v>0.16</v>
       </c>
-      <c r="W169" t="n">
-        <v>3</v>
-      </c>
-      <c r="X169" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y169" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z169" t="n">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>